--- a/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/importTemplate.xlsx
+++ b/spring-boot-starter-module/spring-boot-starter-components/spring-boot-starter-excel/importTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19950" windowHeight="12080"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
-    <t>用户导入</t>
+    <t>客户数据导入模板</t>
   </si>
   <si>
     <t>姓名</t>
@@ -211,17 +211,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -399,7 +392,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,7 +401,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,12 +455,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -605,12 +592,49 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -731,169 +755,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1428,49 +1458,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="21.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" ht="37.5" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
     </row>
-    <row r="2" ht="17.5" spans="1:6">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="18.75" spans="1:6">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="14.5" spans="1:6">
-      <c r="A3" s="5" t="s">
+    <row r="3" ht="15" spans="1:6">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1486,11 +1516,11 @@
         <v>12123123</v>
       </c>
     </row>
-    <row r="4" ht="14.5" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="4" ht="15" spans="1:6">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
